--- a/data/trans_bre/IP7_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP7_R-Clase-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,0; -0,23</t>
+          <t>-6,08; -0,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,66</t>
+          <t>0,0; 4,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 0,0</t>
+          <t>-4,41; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 4,73</t>
+          <t>-2,84; 4,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 3,34</t>
+          <t>-4,25; 3,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 2,16</t>
+          <t>-2,61; 2,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 0,79</t>
+          <t>-3,85; 1,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 4,91</t>
+          <t>-4,28; 5,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 0,71</t>
+          <t>-6,11; 0,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,36</t>
+          <t>0,0; 5,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 7,2</t>
+          <t>-2,04; 7,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 0,0</t>
+          <t>-7,92; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 1,62</t>
+          <t>-2,71; 1,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 1,8</t>
+          <t>-3,86; 1,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 1,35</t>
+          <t>-3,9; 1,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 11,74</t>
+          <t>-2,01; 13,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-82,35; 203,88</t>
+          <t>-86,06; 167,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-70,92; 78,93</t>
+          <t>-68,18; 81,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-80,12; 118,31</t>
+          <t>-84,54; 135,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,85; 965,96</t>
+          <t>-66,63; 896,96</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 1,28</t>
+          <t>-6,03; 1,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 3,8</t>
+          <t>-2,28; 3,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 5,39</t>
+          <t>-1,88; 5,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 4,3</t>
+          <t>-2,59; 4,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-89,35; 73,21</t>
+          <t>-89,28; 80,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-76,68; 402,47</t>
+          <t>-78,51; 409,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-49,34; 611,43</t>
+          <t>-57,15; 618,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-73,6; 570,08</t>
+          <t>-78,05; 465,28</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,48; -0,88</t>
+          <t>-10,69; -1,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 10,3</t>
+          <t>-2,24; 10,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 5,15</t>
+          <t>-1,87; 5,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 6,47</t>
+          <t>-4,18; 6,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>-74,68; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,32; -0,61</t>
+          <t>-3,29; -0,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 1,61</t>
+          <t>-1,33; 1,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 1,28</t>
+          <t>-1,43; 1,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 4,0</t>
+          <t>-0,98; 3,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-76,26; -18,54</t>
+          <t>-78,28; -16,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-37,96; 97,97</t>
+          <t>-43,36; 88,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-48,3; 96,84</t>
+          <t>-51,71; 76,43</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-36,15; 211,21</t>
+          <t>-36,37; 198,61</t>
         </is>
       </c>
     </row>
